--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1569,6 +1569,5381 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118916495</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97869</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>533459</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6831324</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118916563</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>533835</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6831191</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118916503</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56502</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>533551</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6831256</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118916538</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>533361</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6831321</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 blommande.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118916505</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56502</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>533330</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6831362</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118916536</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vitmossamyren, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>533335</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6831217</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>10 blommande</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118916540</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>533370</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6831353</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118916497</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97869</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>533366</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6831375</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118916515</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97867</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>533342</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6831321</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118916525</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>533807</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6831175</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118916522</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>533734</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6831167</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118916533</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>533803</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6831153</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>5 blommande.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118916528</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97750</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>533643</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6831218</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118916498</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97869</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>533378</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6831359</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>8 blommande.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118916499</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97869</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>533418</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6831358</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118916531</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Grustaget, Bläckhornsvägen, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>533488</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6831349</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>12 blommande</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118916506</v>
+      </c>
+      <c r="B26" t="n">
+        <v>103349</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>533367</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6831370</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118916524</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>533742</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6831175</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118916514</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97867</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>533735</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6831167</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>118916551</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>533202</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6831238</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118916543</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>533408</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6831362</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>35 blommande.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118916513</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97867</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>533654</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6831286</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118916530</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>533541</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6831281</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1 blommande.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>118916541</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>533394</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6831359</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118916496</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97869</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>533706</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6831172</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>118916526</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>533233</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6831210</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118916527</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79565</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>533429</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6831320</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118916519</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97880</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Grustaget, Bläckhornsvägen, Hls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>533490</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6831352</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118916558</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>533706</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6831271</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118916516</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97867</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>533391</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6831356</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>118916520</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97880</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>533754</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6831162</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Under gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>118916504</v>
+      </c>
+      <c r="B41" t="n">
+        <v>56502</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>533329</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6831299</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>118916559</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>533639</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6831171</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i dike.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>118916550</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>533799</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6831165</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>118916549</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>533754</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6831152</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>118916560</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>533732</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6831163</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>118916553</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>533388</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6831360</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118916537</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vitmossamyren, Hls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>533332</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6831225</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118916552</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>533316</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6831283</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>118916562</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>533755</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6831181</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>118916532</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>533718</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6831195</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>118916546</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>533428</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6831326</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>16 blommande.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>118916517</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97867</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>533438</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6831363</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>118916565</v>
+      </c>
+      <c r="B53" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>533438</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6831366</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>118916535</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>533413</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6831326</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>5 blommande</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>118916539</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lindsbergsmyrabäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>533379</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6831342</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>15 blommande.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916495</v>
+        <v>118916506</v>
       </c>
       <c r="B10" t="n">
-        <v>97869</v>
+        <v>103349</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533459</v>
+        <v>533367</v>
       </c>
       <c r="R10" t="n">
-        <v>6831324</v>
+        <v>6831370</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1645,22 +1645,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916563</v>
+        <v>118916540</v>
       </c>
       <c r="B11" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,25 +1699,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533835</v>
+        <v>533370</v>
       </c>
       <c r="R11" t="n">
-        <v>6831191</v>
+        <v>6831353</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1757,22 +1757,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916503</v>
+        <v>118916559</v>
       </c>
       <c r="B12" t="n">
-        <v>56502</v>
+        <v>97763</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,38 +1820,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533551</v>
+        <v>533639</v>
       </c>
       <c r="R12" t="n">
-        <v>6831256</v>
+        <v>6831171</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1878,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1888,7 +1889,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i dike.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,10 +1921,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916538</v>
+        <v>118916503</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>56502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,30 +1933,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1959,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533361</v>
+        <v>533551</v>
       </c>
       <c r="R13" t="n">
-        <v>6831321</v>
+        <v>6831256</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1989,27 +1995,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 blommande.</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916505</v>
+        <v>118916552</v>
       </c>
       <c r="B14" t="n">
-        <v>56502</v>
+        <v>78484</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,43 +2049,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533330</v>
+        <v>533316</v>
       </c>
       <c r="R14" t="n">
-        <v>6831362</v>
+        <v>6831283</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2116,7 +2112,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2122,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2149,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916536</v>
+        <v>118916517</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,42 +2161,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vitmossamyren, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533335</v>
+        <v>533438</v>
       </c>
       <c r="R15" t="n">
-        <v>6831217</v>
+        <v>6831363</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2232,7 +2224,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,12 +2234,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>10 blommande</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2261,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916540</v>
+        <v>118916528</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>97750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,38 +2273,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533370</v>
+        <v>533643</v>
       </c>
       <c r="R16" t="n">
-        <v>6831353</v>
+        <v>6831218</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2344,27 +2335,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>4 blommande.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,7 +2377,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916497</v>
+        <v>118916498</v>
       </c>
       <c r="B17" t="n">
         <v>97869</v>
@@ -2426,7 +2412,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2435,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533366</v>
+        <v>533378</v>
       </c>
       <c r="R17" t="n">
-        <v>6831375</v>
+        <v>6831359</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2470,7 +2456,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,7 +2466,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>8 blommande.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916515</v>
+        <v>118916505</v>
       </c>
       <c r="B18" t="n">
-        <v>97867</v>
+        <v>56502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,34 +2514,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533342</v>
+        <v>533330</v>
       </c>
       <c r="R18" t="n">
-        <v>6831321</v>
+        <v>6831362</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2582,7 +2578,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2592,7 +2588,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,10 +2615,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916525</v>
+        <v>118916539</v>
       </c>
       <c r="B19" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2631,38 +2627,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533807</v>
+        <v>533379</v>
       </c>
       <c r="R19" t="n">
-        <v>6831175</v>
+        <v>6831342</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2689,22 +2689,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>15 blommande.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,10 +2736,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118916522</v>
+        <v>118916563</v>
       </c>
       <c r="B20" t="n">
-        <v>79565</v>
+        <v>97763</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2743,25 +2748,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2771,10 +2776,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533734</v>
+        <v>533835</v>
       </c>
       <c r="R20" t="n">
-        <v>6831167</v>
+        <v>6831191</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2806,7 +2811,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2816,7 +2821,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,21 +2832,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2858,10 +2848,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118916533</v>
+        <v>118916558</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>97763</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2870,42 +2860,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533803</v>
+        <v>533706</v>
       </c>
       <c r="R21" t="n">
-        <v>6831153</v>
+        <v>6831271</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2937,7 +2923,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,12 +2933,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>5 blommande.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,10 +2960,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118916528</v>
+        <v>118916533</v>
       </c>
       <c r="B22" t="n">
-        <v>97750</v>
+        <v>97846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,30 +2972,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3023,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533643</v>
+        <v>533803</v>
       </c>
       <c r="R22" t="n">
-        <v>6831218</v>
+        <v>6831153</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3058,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3068,7 +3049,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 blommande.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3095,10 +3081,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118916498</v>
+        <v>118916562</v>
       </c>
       <c r="B23" t="n">
-        <v>97869</v>
+        <v>97763</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,38 +3097,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533378</v>
+        <v>533755</v>
       </c>
       <c r="R23" t="n">
-        <v>6831359</v>
+        <v>6831181</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3169,27 +3151,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>8 blommande.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,7 +3193,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118916499</v>
+        <v>118916497</v>
       </c>
       <c r="B24" t="n">
         <v>97869</v>
@@ -3251,7 +3228,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3260,10 +3237,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533418</v>
+        <v>533366</v>
       </c>
       <c r="R24" t="n">
-        <v>6831358</v>
+        <v>6831375</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3295,7 +3272,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3305,7 +3282,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3453,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118916506</v>
+        <v>118916553</v>
       </c>
       <c r="B26" t="n">
-        <v>103349</v>
+        <v>78484</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3465,42 +3442,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533367</v>
+        <v>533388</v>
       </c>
       <c r="R26" t="n">
-        <v>6831370</v>
+        <v>6831360</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3532,7 +3505,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3542,7 +3515,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,6 +3526,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3569,10 +3557,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118916524</v>
+        <v>118916519</v>
       </c>
       <c r="B27" t="n">
-        <v>79565</v>
+        <v>97880</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,38 +3569,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Grustaget, Bläckhornsvägen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533742</v>
+        <v>533490</v>
       </c>
       <c r="R27" t="n">
-        <v>6831175</v>
+        <v>6831352</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3644,7 +3636,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3646,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,21 +3657,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3696,10 +3673,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118916514</v>
+        <v>118916530</v>
       </c>
       <c r="B28" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3708,38 +3685,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533735</v>
+        <v>533541</v>
       </c>
       <c r="R28" t="n">
-        <v>6831167</v>
+        <v>6831281</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3771,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3781,7 +3762,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 blommande.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3808,10 +3794,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118916551</v>
+        <v>118916524</v>
       </c>
       <c r="B29" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3824,21 +3810,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3848,10 +3834,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533202</v>
+        <v>533742</v>
       </c>
       <c r="R29" t="n">
-        <v>6831238</v>
+        <v>6831175</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3878,22 +3864,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3904,6 +3890,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3920,10 +3921,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118916543</v>
+        <v>118916520</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>97880</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3932,42 +3933,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533408</v>
+        <v>533754</v>
       </c>
       <c r="R30" t="n">
-        <v>6831362</v>
+        <v>6831162</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3994,27 +3991,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>35 blommande.</t>
+          <t>Under gammal sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4041,10 +4038,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118916513</v>
+        <v>118916565</v>
       </c>
       <c r="B31" t="n">
-        <v>97867</v>
+        <v>97763</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4057,34 +4054,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533654</v>
+        <v>533438</v>
       </c>
       <c r="R31" t="n">
-        <v>6831286</v>
+        <v>6831366</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4111,22 +4112,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4153,10 +4154,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118916530</v>
+        <v>118916551</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4165,42 +4166,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533541</v>
+        <v>533202</v>
       </c>
       <c r="R32" t="n">
-        <v>6831281</v>
+        <v>6831238</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4227,27 +4224,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>1 blommande.</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4274,10 +4266,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118916541</v>
+        <v>118916522</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4286,42 +4278,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533394</v>
+        <v>533734</v>
       </c>
       <c r="R33" t="n">
-        <v>6831359</v>
+        <v>6831167</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4348,27 +4336,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>4 blommande.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4379,6 +4362,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4395,7 +4393,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118916496</v>
+        <v>118916499</v>
       </c>
       <c r="B34" t="n">
         <v>97869</v>
@@ -4439,10 +4437,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533706</v>
+        <v>533418</v>
       </c>
       <c r="R34" t="n">
-        <v>6831172</v>
+        <v>6831358</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4469,22 +4467,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4511,10 +4509,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118916526</v>
+        <v>118916537</v>
       </c>
       <c r="B35" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4523,38 +4521,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Vitmossamyren, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533233</v>
+        <v>533332</v>
       </c>
       <c r="R35" t="n">
-        <v>6831210</v>
+        <v>6831225</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4586,7 +4588,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4596,7 +4598,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4623,10 +4630,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118916527</v>
+        <v>118916532</v>
       </c>
       <c r="B36" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4635,38 +4642,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533429</v>
+        <v>533718</v>
       </c>
       <c r="R36" t="n">
-        <v>6831320</v>
+        <v>6831195</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4693,22 +4704,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4735,10 +4746,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118916519</v>
+        <v>118916550</v>
       </c>
       <c r="B37" t="n">
-        <v>97880</v>
+        <v>78484</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4747,42 +4758,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grustaget, Bläckhornsvägen, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533490</v>
+        <v>533799</v>
       </c>
       <c r="R37" t="n">
-        <v>6831352</v>
+        <v>6831165</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4814,7 +4821,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4824,7 +4831,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4851,10 +4858,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118916558</v>
+        <v>118916527</v>
       </c>
       <c r="B38" t="n">
-        <v>97763</v>
+        <v>79565</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4863,25 +4870,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4891,10 +4898,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533706</v>
+        <v>533429</v>
       </c>
       <c r="R38" t="n">
-        <v>6831271</v>
+        <v>6831320</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4921,22 +4928,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4963,10 +4970,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118916516</v>
+        <v>118916541</v>
       </c>
       <c r="B39" t="n">
-        <v>97867</v>
+        <v>97846</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4975,38 +4982,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533391</v>
+        <v>533394</v>
       </c>
       <c r="R39" t="n">
-        <v>6831356</v>
+        <v>6831359</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5038,7 +5049,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5048,12 +5059,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Riklig förekomst.</t>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5080,10 +5091,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118916520</v>
+        <v>118916526</v>
       </c>
       <c r="B40" t="n">
-        <v>97880</v>
+        <v>79565</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5092,25 +5103,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5120,10 +5131,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533754</v>
+        <v>533233</v>
       </c>
       <c r="R40" t="n">
-        <v>6831162</v>
+        <v>6831210</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5150,27 +5161,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Under gammal sälg.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5197,10 +5203,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118916504</v>
+        <v>118916560</v>
       </c>
       <c r="B41" t="n">
-        <v>56502</v>
+        <v>97763</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5213,39 +5219,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533329</v>
+        <v>533732</v>
       </c>
       <c r="R41" t="n">
-        <v>6831299</v>
+        <v>6831163</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5272,22 +5273,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5314,10 +5315,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118916559</v>
+        <v>118916535</v>
       </c>
       <c r="B42" t="n">
-        <v>97763</v>
+        <v>97846</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5326,38 +5327,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533639</v>
+        <v>533413</v>
       </c>
       <c r="R42" t="n">
-        <v>6831171</v>
+        <v>6831326</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5384,27 +5389,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Riklig förekomst i dike.</t>
+          <t>5 blommande</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5431,10 +5436,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118916550</v>
+        <v>118916538</v>
       </c>
       <c r="B43" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5443,38 +5448,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533799</v>
+        <v>533361</v>
       </c>
       <c r="R43" t="n">
-        <v>6831165</v>
+        <v>6831321</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5501,22 +5510,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 blommande.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5543,10 +5557,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118916549</v>
+        <v>118916504</v>
       </c>
       <c r="B44" t="n">
-        <v>78484</v>
+        <v>56502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5555,38 +5569,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533754</v>
+        <v>533329</v>
       </c>
       <c r="R44" t="n">
-        <v>6831152</v>
+        <v>6831299</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5613,7 +5632,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -5623,7 +5642,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -5655,10 +5674,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118916560</v>
+        <v>118916496</v>
       </c>
       <c r="B45" t="n">
-        <v>97763</v>
+        <v>97869</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5671,34 +5690,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533732</v>
+        <v>533706</v>
       </c>
       <c r="R45" t="n">
-        <v>6831163</v>
+        <v>6831172</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5730,7 +5753,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5740,7 +5763,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5767,10 +5790,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118916553</v>
+        <v>118916495</v>
       </c>
       <c r="B46" t="n">
-        <v>78484</v>
+        <v>97869</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5779,38 +5802,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533388</v>
+        <v>533459</v>
       </c>
       <c r="R46" t="n">
-        <v>6831360</v>
+        <v>6831324</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5837,22 +5864,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5863,21 +5890,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5894,10 +5906,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118916537</v>
+        <v>118916513</v>
       </c>
       <c r="B47" t="n">
-        <v>97846</v>
+        <v>97867</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5906,42 +5918,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vitmossamyren, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533332</v>
+        <v>533654</v>
       </c>
       <c r="R47" t="n">
-        <v>6831225</v>
+        <v>6831286</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5968,27 +5976,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>4 blommande.</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6015,10 +6018,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118916552</v>
+        <v>118916516</v>
       </c>
       <c r="B48" t="n">
-        <v>78484</v>
+        <v>97867</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6027,25 +6030,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6055,10 +6058,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533316</v>
+        <v>533391</v>
       </c>
       <c r="R48" t="n">
-        <v>6831283</v>
+        <v>6831356</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6090,7 +6093,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6100,7 +6103,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6127,10 +6135,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118916562</v>
+        <v>118916514</v>
       </c>
       <c r="B49" t="n">
-        <v>97763</v>
+        <v>97867</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6143,21 +6151,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6167,10 +6175,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533755</v>
+        <v>533735</v>
       </c>
       <c r="R49" t="n">
-        <v>6831181</v>
+        <v>6831167</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6202,7 +6210,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6212,7 +6220,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6239,10 +6247,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118916532</v>
+        <v>118916525</v>
       </c>
       <c r="B50" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6251,42 +6259,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533718</v>
+        <v>533807</v>
       </c>
       <c r="R50" t="n">
-        <v>6831195</v>
+        <v>6831175</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6318,7 +6322,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6328,7 +6332,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6355,7 +6359,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118916546</v>
+        <v>118916536</v>
       </c>
       <c r="B51" t="n">
         <v>97846</v>
@@ -6390,19 +6394,19 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Vitmossamyren, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533428</v>
+        <v>533335</v>
       </c>
       <c r="R51" t="n">
-        <v>6831326</v>
+        <v>6831217</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6434,7 +6438,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6444,12 +6448,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>16 blommande.</t>
+          <t>10 blommande</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6476,10 +6480,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118916517</v>
+        <v>118916549</v>
       </c>
       <c r="B52" t="n">
-        <v>97867</v>
+        <v>78484</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6488,25 +6492,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6516,10 +6520,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533438</v>
+        <v>533754</v>
       </c>
       <c r="R52" t="n">
-        <v>6831363</v>
+        <v>6831152</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6546,22 +6550,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6588,10 +6592,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118916565</v>
+        <v>118916515</v>
       </c>
       <c r="B53" t="n">
-        <v>97763</v>
+        <v>97867</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6604,38 +6608,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533438</v>
+        <v>533342</v>
       </c>
       <c r="R53" t="n">
-        <v>6831366</v>
+        <v>6831321</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6704,7 +6704,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118916535</v>
+        <v>118916546</v>
       </c>
       <c r="B54" t="n">
         <v>97846</v>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533413</v>
+        <v>533428</v>
       </c>
       <c r="R54" t="n">
         <v>6831326</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>5 blommande</t>
+          <t>16 blommande.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6825,7 +6825,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118916539</v>
+        <v>118916543</v>
       </c>
       <c r="B55" t="n">
         <v>97846</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533379</v>
+        <v>533408</v>
       </c>
       <c r="R55" t="n">
-        <v>6831342</v>
+        <v>6831362</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>15 blommande.</t>
+          <t>35 blommande.</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916506</v>
+        <v>118916541</v>
       </c>
       <c r="B10" t="n">
-        <v>103349</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,30 +1583,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533367</v>
+        <v>533394</v>
       </c>
       <c r="R10" t="n">
-        <v>6831370</v>
+        <v>6831359</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,7 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916540</v>
+        <v>118916499</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97876</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,38 +1704,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533370</v>
+        <v>533418</v>
       </c>
       <c r="R11" t="n">
-        <v>6831353</v>
+        <v>6831358</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1762,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1772,12 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4 blommande.</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916559</v>
+        <v>118916517</v>
       </c>
       <c r="B12" t="n">
-        <v>97763</v>
+        <v>97874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,21 +1824,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533639</v>
+        <v>533438</v>
       </c>
       <c r="R12" t="n">
-        <v>6831171</v>
+        <v>6831363</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1874,27 +1878,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i dike.</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,10 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916503</v>
+        <v>118916515</v>
       </c>
       <c r="B13" t="n">
-        <v>56502</v>
+        <v>97874</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,38 +1936,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533551</v>
+        <v>533342</v>
       </c>
       <c r="R13" t="n">
-        <v>6831256</v>
+        <v>6831321</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1995,22 +1990,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916552</v>
+        <v>118916531</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,38 +2044,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Grustaget, Bläckhornsvägen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533316</v>
+        <v>533488</v>
       </c>
       <c r="R14" t="n">
-        <v>6831283</v>
+        <v>6831349</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2107,22 +2106,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>12 blommande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2149,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916517</v>
+        <v>118916535</v>
       </c>
       <c r="B15" t="n">
-        <v>97867</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,38 +2165,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533438</v>
+        <v>533413</v>
       </c>
       <c r="R15" t="n">
-        <v>6831363</v>
+        <v>6831326</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2224,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2234,7 +2242,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5 blommande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2261,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916528</v>
+        <v>118916538</v>
       </c>
       <c r="B16" t="n">
-        <v>97750</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,30 +2286,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2305,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533643</v>
+        <v>533361</v>
       </c>
       <c r="R16" t="n">
-        <v>6831218</v>
+        <v>6831321</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2335,22 +2348,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 blommande.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916498</v>
+        <v>118916528</v>
       </c>
       <c r="B17" t="n">
-        <v>97869</v>
+        <v>97757</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,26 +2411,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219847</v>
+        <v>220093</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2421,10 +2439,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533378</v>
+        <v>533643</v>
       </c>
       <c r="R17" t="n">
-        <v>6831359</v>
+        <v>6831218</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2451,27 +2469,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>8 blommande.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916505</v>
+        <v>118916497</v>
       </c>
       <c r="B18" t="n">
-        <v>56502</v>
+        <v>97876</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,27 +2527,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2543,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533330</v>
+        <v>533366</v>
       </c>
       <c r="R18" t="n">
-        <v>6831362</v>
+        <v>6831375</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2578,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2588,7 +2600,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2615,10 +2627,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916539</v>
+        <v>118916520</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>97887</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2627,42 +2639,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533379</v>
+        <v>533754</v>
       </c>
       <c r="R19" t="n">
-        <v>6831342</v>
+        <v>6831162</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2689,27 +2697,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>15 blommande.</t>
+          <t>Under gammal sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,10 +2744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118916563</v>
+        <v>118916560</v>
       </c>
       <c r="B20" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2776,10 +2784,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533835</v>
+        <v>533732</v>
       </c>
       <c r="R20" t="n">
-        <v>6831191</v>
+        <v>6831163</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2811,7 +2819,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2821,7 +2829,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,10 +2856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118916558</v>
+        <v>118916536</v>
       </c>
       <c r="B21" t="n">
-        <v>97763</v>
+        <v>97853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2860,38 +2868,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Vitmossamyren, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533706</v>
+        <v>533335</v>
       </c>
       <c r="R21" t="n">
-        <v>6831271</v>
+        <v>6831217</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2918,22 +2930,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10 blommande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2960,10 +2977,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118916533</v>
+        <v>118916546</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2995,7 +3012,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3004,10 +3021,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533803</v>
+        <v>533428</v>
       </c>
       <c r="R22" t="n">
-        <v>6831153</v>
+        <v>6831326</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3034,27 +3051,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>5 blommande.</t>
+          <t>16 blommande.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3081,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118916562</v>
+        <v>118916543</v>
       </c>
       <c r="B23" t="n">
-        <v>97763</v>
+        <v>97853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3093,38 +3110,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533755</v>
+        <v>533408</v>
       </c>
       <c r="R23" t="n">
-        <v>6831181</v>
+        <v>6831362</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3151,22 +3172,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>35 blommande.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,10 +3219,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118916497</v>
+        <v>118916551</v>
       </c>
       <c r="B24" t="n">
-        <v>97869</v>
+        <v>78491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3205,42 +3231,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533366</v>
+        <v>533202</v>
       </c>
       <c r="R24" t="n">
-        <v>6831375</v>
+        <v>6831238</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3272,7 +3294,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3282,7 +3304,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,10 +3331,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118916531</v>
+        <v>118916504</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>56502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3321,42 +3343,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>130</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grustaget, Bläckhornsvägen, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533488</v>
+        <v>533329</v>
       </c>
       <c r="R25" t="n">
-        <v>6831349</v>
+        <v>6831299</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3383,27 +3406,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>12 blommande</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3430,10 +3448,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118916553</v>
+        <v>118916563</v>
       </c>
       <c r="B26" t="n">
-        <v>78484</v>
+        <v>97770</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3442,25 +3460,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3470,10 +3488,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533388</v>
+        <v>533835</v>
       </c>
       <c r="R26" t="n">
-        <v>6831360</v>
+        <v>6831191</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3500,22 +3518,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,21 +3544,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3560,7 +3563,7 @@
         <v>118916519</v>
       </c>
       <c r="B27" t="n">
-        <v>97880</v>
+        <v>97887</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3673,10 +3676,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118916530</v>
+        <v>118916558</v>
       </c>
       <c r="B28" t="n">
-        <v>97846</v>
+        <v>97770</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3685,42 +3688,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533541</v>
+        <v>533706</v>
       </c>
       <c r="R28" t="n">
-        <v>6831281</v>
+        <v>6831271</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3752,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,12 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>1 blommande.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3794,10 +3788,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118916524</v>
+        <v>118916516</v>
       </c>
       <c r="B29" t="n">
-        <v>79565</v>
+        <v>97874</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3806,25 +3800,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3834,10 +3828,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533742</v>
+        <v>533391</v>
       </c>
       <c r="R29" t="n">
-        <v>6831175</v>
+        <v>6831356</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3864,22 +3858,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3890,21 +3889,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3921,10 +3905,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118916520</v>
+        <v>118916495</v>
       </c>
       <c r="B30" t="n">
-        <v>97880</v>
+        <v>97876</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,34 +3921,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533754</v>
+        <v>533459</v>
       </c>
       <c r="R30" t="n">
-        <v>6831162</v>
+        <v>6831324</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3996,7 +3984,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4006,12 +3994,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Under gammal sälg.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4038,10 +4021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118916565</v>
+        <v>118916559</v>
       </c>
       <c r="B31" t="n">
-        <v>97763</v>
+        <v>97770</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4071,21 +4054,17 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533438</v>
+        <v>533639</v>
       </c>
       <c r="R31" t="n">
-        <v>6831366</v>
+        <v>6831171</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4112,22 +4091,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i dike.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4154,10 +4138,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118916551</v>
+        <v>118916530</v>
       </c>
       <c r="B32" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4166,38 +4150,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533202</v>
+        <v>533541</v>
       </c>
       <c r="R32" t="n">
-        <v>6831238</v>
+        <v>6831281</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4224,22 +4212,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1 blommande.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4266,10 +4259,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118916522</v>
+        <v>118916533</v>
       </c>
       <c r="B33" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4278,38 +4271,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533734</v>
+        <v>533803</v>
       </c>
       <c r="R33" t="n">
-        <v>6831167</v>
+        <v>6831153</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4341,7 +4338,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4351,7 +4348,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>5 blommande.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4362,21 +4364,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4393,10 +4380,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118916499</v>
+        <v>118916550</v>
       </c>
       <c r="B34" t="n">
-        <v>97869</v>
+        <v>78491</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4405,42 +4392,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533418</v>
+        <v>533799</v>
       </c>
       <c r="R34" t="n">
-        <v>6831358</v>
+        <v>6831165</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4467,22 +4450,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4509,10 +4492,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118916537</v>
+        <v>118916513</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>97874</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4521,42 +4504,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vitmossamyren, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533332</v>
+        <v>533654</v>
       </c>
       <c r="R35" t="n">
-        <v>6831225</v>
+        <v>6831286</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4583,27 +4562,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>4 blommande.</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4630,10 +4604,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118916532</v>
+        <v>118916522</v>
       </c>
       <c r="B36" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4642,42 +4616,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533718</v>
+        <v>533734</v>
       </c>
       <c r="R36" t="n">
-        <v>6831195</v>
+        <v>6831167</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4709,7 +4679,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4719,7 +4689,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4730,6 +4700,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4746,10 +4731,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118916550</v>
+        <v>118916527</v>
       </c>
       <c r="B37" t="n">
-        <v>78484</v>
+        <v>79572</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4762,21 +4747,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4786,10 +4771,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533799</v>
+        <v>533429</v>
       </c>
       <c r="R37" t="n">
-        <v>6831165</v>
+        <v>6831320</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4816,22 +4801,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4858,10 +4843,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118916527</v>
+        <v>118916549</v>
       </c>
       <c r="B38" t="n">
-        <v>79565</v>
+        <v>78491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4874,21 +4859,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4898,10 +4883,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533429</v>
+        <v>533754</v>
       </c>
       <c r="R38" t="n">
-        <v>6831320</v>
+        <v>6831152</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4928,22 +4913,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4970,10 +4955,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118916541</v>
+        <v>118916565</v>
       </c>
       <c r="B39" t="n">
-        <v>97846</v>
+        <v>97770</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4982,30 +4967,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5014,10 +4999,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533394</v>
+        <v>533438</v>
       </c>
       <c r="R39" t="n">
-        <v>6831359</v>
+        <v>6831366</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5049,7 +5034,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5059,12 +5044,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>4 blommande.</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5091,10 +5071,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118916526</v>
+        <v>118916498</v>
       </c>
       <c r="B40" t="n">
-        <v>79565</v>
+        <v>97876</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5103,38 +5083,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533233</v>
+        <v>533378</v>
       </c>
       <c r="R40" t="n">
-        <v>6831210</v>
+        <v>6831359</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5166,7 +5150,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5176,7 +5160,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>8 blommande.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5203,10 +5192,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118916560</v>
+        <v>118916525</v>
       </c>
       <c r="B41" t="n">
-        <v>97763</v>
+        <v>79572</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5215,25 +5204,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5243,10 +5232,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533732</v>
+        <v>533807</v>
       </c>
       <c r="R41" t="n">
-        <v>6831163</v>
+        <v>6831175</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5278,7 +5267,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5288,7 +5277,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5315,10 +5304,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118916535</v>
+        <v>118916539</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5350,7 +5339,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5359,10 +5348,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533413</v>
+        <v>533379</v>
       </c>
       <c r="R42" t="n">
-        <v>6831326</v>
+        <v>6831342</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5394,7 +5383,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5404,12 +5393,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>5 blommande</t>
+          <t>15 blommande.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5436,10 +5425,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118916538</v>
+        <v>118916562</v>
       </c>
       <c r="B43" t="n">
-        <v>97846</v>
+        <v>97770</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5448,42 +5437,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533361</v>
+        <v>533755</v>
       </c>
       <c r="R43" t="n">
-        <v>6831321</v>
+        <v>6831181</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5510,27 +5495,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1 blommande.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5557,10 +5537,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118916504</v>
+        <v>118916540</v>
       </c>
       <c r="B44" t="n">
-        <v>56502</v>
+        <v>97853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5569,43 +5549,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533329</v>
+        <v>533370</v>
       </c>
       <c r="R44" t="n">
-        <v>6831299</v>
+        <v>6831353</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5637,7 +5612,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5647,7 +5622,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5674,10 +5654,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118916496</v>
+        <v>118916532</v>
       </c>
       <c r="B45" t="n">
-        <v>97869</v>
+        <v>97853</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5686,30 +5666,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5718,10 +5698,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533706</v>
+        <v>533718</v>
       </c>
       <c r="R45" t="n">
-        <v>6831172</v>
+        <v>6831195</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5753,7 +5733,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5763,7 +5743,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5790,10 +5770,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118916495</v>
+        <v>118916496</v>
       </c>
       <c r="B46" t="n">
-        <v>97869</v>
+        <v>97876</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5825,7 +5805,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5834,10 +5814,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533459</v>
+        <v>533706</v>
       </c>
       <c r="R46" t="n">
-        <v>6831324</v>
+        <v>6831172</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5869,7 +5849,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5879,7 +5859,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5906,10 +5886,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118916513</v>
+        <v>118916505</v>
       </c>
       <c r="B47" t="n">
-        <v>97867</v>
+        <v>56502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5922,34 +5902,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533654</v>
+        <v>533330</v>
       </c>
       <c r="R47" t="n">
-        <v>6831286</v>
+        <v>6831362</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5976,22 +5961,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6018,10 +6003,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118916516</v>
+        <v>118916526</v>
       </c>
       <c r="B48" t="n">
-        <v>97867</v>
+        <v>79572</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6030,25 +6015,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6058,10 +6043,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533391</v>
+        <v>533233</v>
       </c>
       <c r="R48" t="n">
-        <v>6831356</v>
+        <v>6831210</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6093,7 +6078,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6103,12 +6088,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6135,10 +6115,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118916514</v>
+        <v>118916537</v>
       </c>
       <c r="B49" t="n">
-        <v>97867</v>
+        <v>97853</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6147,38 +6127,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Vitmossamyren, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533735</v>
+        <v>533332</v>
       </c>
       <c r="R49" t="n">
-        <v>6831167</v>
+        <v>6831225</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6205,22 +6189,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6247,10 +6236,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118916525</v>
+        <v>118916552</v>
       </c>
       <c r="B50" t="n">
-        <v>79565</v>
+        <v>78491</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6263,21 +6252,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6287,10 +6276,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533807</v>
+        <v>533316</v>
       </c>
       <c r="R50" t="n">
-        <v>6831175</v>
+        <v>6831283</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6317,22 +6306,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6359,10 +6348,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118916536</v>
+        <v>118916524</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
+        <v>79572</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6371,42 +6360,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vitmossamyren, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533335</v>
+        <v>533742</v>
       </c>
       <c r="R51" t="n">
-        <v>6831217</v>
+        <v>6831175</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6433,27 +6418,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>10 blommande</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6464,6 +6444,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6480,10 +6475,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118916549</v>
+        <v>118916503</v>
       </c>
       <c r="B52" t="n">
-        <v>78484</v>
+        <v>56502</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6492,38 +6487,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533754</v>
+        <v>533551</v>
       </c>
       <c r="R52" t="n">
-        <v>6831152</v>
+        <v>6831256</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6555,7 +6554,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6565,7 +6564,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6592,10 +6591,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118916515</v>
+        <v>118916514</v>
       </c>
       <c r="B53" t="n">
-        <v>97867</v>
+        <v>97874</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6632,10 +6631,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533342</v>
+        <v>533735</v>
       </c>
       <c r="R53" t="n">
-        <v>6831321</v>
+        <v>6831167</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6662,7 +6661,7 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -6672,7 +6671,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -6704,10 +6703,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118916546</v>
+        <v>118916506</v>
       </c>
       <c r="B54" t="n">
-        <v>97846</v>
+        <v>103356</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6716,30 +6715,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6748,10 +6747,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533428</v>
+        <v>533367</v>
       </c>
       <c r="R54" t="n">
-        <v>6831326</v>
+        <v>6831370</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6783,7 +6782,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6793,12 +6792,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>16 blommande.</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6825,10 +6819,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118916543</v>
+        <v>118916553</v>
       </c>
       <c r="B55" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6837,42 +6831,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533408</v>
+        <v>533388</v>
       </c>
       <c r="R55" t="n">
-        <v>6831362</v>
+        <v>6831360</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6904,7 +6894,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6914,12 +6904,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>35 blommande.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6930,6 +6915,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916531</v>
+        <v>118916528</v>
       </c>
       <c r="B14" t="n">
-        <v>97853</v>
+        <v>97757</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,42 +2044,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grustaget, Bläckhornsvägen, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533488</v>
+        <v>533643</v>
       </c>
       <c r="R14" t="n">
-        <v>6831349</v>
+        <v>6831218</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,12 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>12 blommande</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916535</v>
+        <v>118916497</v>
       </c>
       <c r="B15" t="n">
-        <v>97853</v>
+        <v>97876</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,30 +2160,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2197,10 +2192,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533413</v>
+        <v>533366</v>
       </c>
       <c r="R15" t="n">
-        <v>6831326</v>
+        <v>6831375</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2232,7 +2227,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,12 +2237,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>5 blommande</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916538</v>
+        <v>118916520</v>
       </c>
       <c r="B16" t="n">
-        <v>97853</v>
+        <v>97887</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,42 +2276,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533361</v>
+        <v>533754</v>
       </c>
       <c r="R16" t="n">
-        <v>6831321</v>
+        <v>6831162</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,27 +2334,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1 blommande.</t>
+          <t>Under gammal sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916528</v>
+        <v>118916531</v>
       </c>
       <c r="B17" t="n">
-        <v>97757</v>
+        <v>97853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,42 +2393,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Grustaget, Bläckhornsvägen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533643</v>
+        <v>533488</v>
       </c>
       <c r="R17" t="n">
-        <v>6831218</v>
+        <v>6831349</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2474,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2484,7 +2470,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>12 blommande</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2502,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916497</v>
+        <v>118916535</v>
       </c>
       <c r="B18" t="n">
-        <v>97876</v>
+        <v>97853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,30 +2514,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2555,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533366</v>
+        <v>533413</v>
       </c>
       <c r="R18" t="n">
-        <v>6831375</v>
+        <v>6831326</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2590,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,7 +2591,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>5 blommande</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2627,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916520</v>
+        <v>118916538</v>
       </c>
       <c r="B19" t="n">
-        <v>97887</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,38 +2635,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533754</v>
+        <v>533361</v>
       </c>
       <c r="R19" t="n">
-        <v>6831162</v>
+        <v>6831321</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2697,27 +2697,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Under gammal sälg.</t>
+          <t>1 blommande.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3098,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118916543</v>
+        <v>118916563</v>
       </c>
       <c r="B23" t="n">
-        <v>97853</v>
+        <v>97770</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3110,42 +3110,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533408</v>
+        <v>533835</v>
       </c>
       <c r="R23" t="n">
-        <v>6831362</v>
+        <v>6831191</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3172,27 +3168,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>35 blommande.</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,10 +3210,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118916551</v>
+        <v>118916519</v>
       </c>
       <c r="B24" t="n">
-        <v>78491</v>
+        <v>97887</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3231,38 +3222,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Grustaget, Bläckhornsvägen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533202</v>
+        <v>533490</v>
       </c>
       <c r="R24" t="n">
-        <v>6831238</v>
+        <v>6831352</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3289,22 +3284,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3331,10 +3326,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118916504</v>
+        <v>118916543</v>
       </c>
       <c r="B25" t="n">
-        <v>56502</v>
+        <v>97853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3343,31 +3338,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>500</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3376,10 +3370,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533329</v>
+        <v>533408</v>
       </c>
       <c r="R25" t="n">
-        <v>6831299</v>
+        <v>6831362</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3411,7 +3405,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3421,7 +3415,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>35 blommande.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3448,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118916563</v>
+        <v>118916551</v>
       </c>
       <c r="B26" t="n">
-        <v>97770</v>
+        <v>78491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,25 +3459,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3488,10 +3487,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533835</v>
+        <v>533202</v>
       </c>
       <c r="R26" t="n">
-        <v>6831191</v>
+        <v>6831238</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3518,22 +3517,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3560,10 +3559,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118916519</v>
+        <v>118916504</v>
       </c>
       <c r="B27" t="n">
-        <v>97887</v>
+        <v>56502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3576,38 +3575,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219874</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grustaget, Bläckhornsvägen, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533490</v>
+        <v>533329</v>
       </c>
       <c r="R27" t="n">
-        <v>6831352</v>
+        <v>6831299</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3634,22 +3634,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4380,10 +4380,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118916550</v>
+        <v>118916513</v>
       </c>
       <c r="B34" t="n">
-        <v>78491</v>
+        <v>97874</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4392,25 +4392,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533799</v>
+        <v>533654</v>
       </c>
       <c r="R34" t="n">
-        <v>6831165</v>
+        <v>6831286</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4492,10 +4492,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118916513</v>
+        <v>118916550</v>
       </c>
       <c r="B35" t="n">
-        <v>97874</v>
+        <v>78491</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4504,25 +4504,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533654</v>
+        <v>533799</v>
       </c>
       <c r="R35" t="n">
-        <v>6831286</v>
+        <v>6831165</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5071,10 +5071,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118916498</v>
+        <v>118916525</v>
       </c>
       <c r="B40" t="n">
-        <v>97876</v>
+        <v>79572</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5083,42 +5083,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533378</v>
+        <v>533807</v>
       </c>
       <c r="R40" t="n">
-        <v>6831359</v>
+        <v>6831175</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5145,27 +5141,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>8 blommande.</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5192,10 +5183,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118916525</v>
+        <v>118916498</v>
       </c>
       <c r="B41" t="n">
-        <v>79572</v>
+        <v>97876</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5204,38 +5195,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533807</v>
+        <v>533378</v>
       </c>
       <c r="R41" t="n">
-        <v>6831175</v>
+        <v>6831359</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5262,22 +5257,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>8 blommande.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916541</v>
+        <v>118916527</v>
       </c>
       <c r="B10" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,42 +1583,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533394</v>
+        <v>533429</v>
       </c>
       <c r="R10" t="n">
-        <v>6831359</v>
+        <v>6831320</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4 blommande.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1808,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916517</v>
+        <v>118916560</v>
       </c>
       <c r="B12" t="n">
-        <v>97874</v>
+        <v>97770</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,21 +1815,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1848,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533438</v>
+        <v>533732</v>
       </c>
       <c r="R12" t="n">
-        <v>6831363</v>
+        <v>6831163</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1878,22 +1869,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916515</v>
+        <v>118916536</v>
       </c>
       <c r="B13" t="n">
-        <v>97874</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,38 +1923,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Vitmossamyren, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533342</v>
+        <v>533335</v>
       </c>
       <c r="R13" t="n">
-        <v>6831321</v>
+        <v>6831217</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1995,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2000,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>10 blommande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916528</v>
+        <v>118916533</v>
       </c>
       <c r="B14" t="n">
-        <v>97757</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,30 +2044,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>110</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533643</v>
+        <v>533803</v>
       </c>
       <c r="R14" t="n">
-        <v>6831218</v>
+        <v>6831153</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2121,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>5 blommande.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916497</v>
+        <v>118916530</v>
       </c>
       <c r="B15" t="n">
-        <v>97876</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,30 +2165,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2192,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533366</v>
+        <v>533541</v>
       </c>
       <c r="R15" t="n">
-        <v>6831375</v>
+        <v>6831281</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2222,22 +2227,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 blommande.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916520</v>
+        <v>118916528</v>
       </c>
       <c r="B16" t="n">
-        <v>97887</v>
+        <v>97757</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,34 +2290,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219874</v>
+        <v>220093</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533754</v>
+        <v>533643</v>
       </c>
       <c r="R16" t="n">
-        <v>6831162</v>
+        <v>6831218</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2339,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2349,12 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Under gammal sälg.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,10 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916531</v>
+        <v>118916565</v>
       </c>
       <c r="B17" t="n">
-        <v>97853</v>
+        <v>97770</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,42 +2402,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grustaget, Bläckhornsvägen, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533488</v>
+        <v>533438</v>
       </c>
       <c r="R17" t="n">
-        <v>6831349</v>
+        <v>6831366</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,27 +2464,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>12 blommande</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916535</v>
+        <v>118916563</v>
       </c>
       <c r="B18" t="n">
-        <v>97853</v>
+        <v>97770</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,42 +2518,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533413</v>
+        <v>533835</v>
       </c>
       <c r="R18" t="n">
-        <v>6831326</v>
+        <v>6831191</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2576,27 +2576,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>5 blommande</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916538</v>
+        <v>118916562</v>
       </c>
       <c r="B19" t="n">
-        <v>97853</v>
+        <v>97770</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2635,42 +2630,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533361</v>
+        <v>533755</v>
       </c>
       <c r="R19" t="n">
-        <v>6831321</v>
+        <v>6831181</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2697,27 +2688,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1 blommande.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118916560</v>
+        <v>118916519</v>
       </c>
       <c r="B20" t="n">
-        <v>97770</v>
+        <v>97887</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2760,34 +2746,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Grustaget, Bläckhornsvägen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533732</v>
+        <v>533490</v>
       </c>
       <c r="R20" t="n">
-        <v>6831163</v>
+        <v>6831352</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2819,7 +2809,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,7 +2819,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2856,10 +2846,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118916536</v>
+        <v>118916505</v>
       </c>
       <c r="B21" t="n">
-        <v>97853</v>
+        <v>56502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,42 +2858,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>110</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vitmossamyren, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533335</v>
+        <v>533330</v>
       </c>
       <c r="R21" t="n">
-        <v>6831217</v>
+        <v>6831362</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2935,7 +2926,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,12 +2936,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>10 blommande</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2977,10 +2963,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118916546</v>
+        <v>118916524</v>
       </c>
       <c r="B22" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2989,42 +2975,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533428</v>
+        <v>533742</v>
       </c>
       <c r="R22" t="n">
-        <v>6831326</v>
+        <v>6831175</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3051,27 +3033,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>16 blommande.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3082,6 +3059,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3098,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118916563</v>
+        <v>118916504</v>
       </c>
       <c r="B23" t="n">
-        <v>97770</v>
+        <v>56502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3114,34 +3106,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533835</v>
+        <v>533329</v>
       </c>
       <c r="R23" t="n">
-        <v>6831191</v>
+        <v>6831299</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3168,22 +3165,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3210,10 +3207,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118916519</v>
+        <v>118916540</v>
       </c>
       <c r="B24" t="n">
-        <v>97887</v>
+        <v>97853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3222,42 +3219,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grustaget, Bläckhornsvägen, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533490</v>
+        <v>533370</v>
       </c>
       <c r="R24" t="n">
-        <v>6831352</v>
+        <v>6831353</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3284,22 +3277,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3326,10 +3324,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118916543</v>
+        <v>118916550</v>
       </c>
       <c r="B25" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3338,42 +3336,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533408</v>
+        <v>533799</v>
       </c>
       <c r="R25" t="n">
-        <v>6831362</v>
+        <v>6831165</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3400,27 +3394,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>35 blommande.</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3447,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118916551</v>
+        <v>118916526</v>
       </c>
       <c r="B26" t="n">
-        <v>78491</v>
+        <v>79572</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,21 +3452,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3476,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533202</v>
+        <v>533233</v>
       </c>
       <c r="R26" t="n">
-        <v>6831238</v>
+        <v>6831210</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3522,7 +3511,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3532,7 +3521,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,10 +3548,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118916504</v>
+        <v>118916525</v>
       </c>
       <c r="B27" t="n">
-        <v>56502</v>
+        <v>79572</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3571,43 +3560,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533329</v>
+        <v>533807</v>
       </c>
       <c r="R27" t="n">
-        <v>6831299</v>
+        <v>6831175</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3634,22 +3618,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3676,10 +3660,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118916558</v>
+        <v>118916543</v>
       </c>
       <c r="B28" t="n">
-        <v>97770</v>
+        <v>97853</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3688,38 +3672,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533706</v>
+        <v>533408</v>
       </c>
       <c r="R28" t="n">
-        <v>6831271</v>
+        <v>6831362</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3746,22 +3734,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>35 blommande.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3788,10 +3781,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118916516</v>
+        <v>118916539</v>
       </c>
       <c r="B29" t="n">
-        <v>97874</v>
+        <v>97853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3800,38 +3793,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533391</v>
+        <v>533379</v>
       </c>
       <c r="R29" t="n">
-        <v>6831356</v>
+        <v>6831342</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3863,7 +3860,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3873,12 +3870,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Riklig förekomst.</t>
+          <t>15 blommande.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3905,10 +3902,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118916495</v>
+        <v>118916522</v>
       </c>
       <c r="B30" t="n">
-        <v>97876</v>
+        <v>79572</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3917,42 +3914,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533459</v>
+        <v>533734</v>
       </c>
       <c r="R30" t="n">
-        <v>6831324</v>
+        <v>6831167</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3984,7 +3977,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3994,7 +3987,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4005,6 +3998,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4021,7 +4029,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118916559</v>
+        <v>118916558</v>
       </c>
       <c r="B31" t="n">
         <v>97770</v>
@@ -4061,10 +4069,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533639</v>
+        <v>533706</v>
       </c>
       <c r="R31" t="n">
-        <v>6831171</v>
+        <v>6831271</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4096,7 +4104,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4106,12 +4114,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i dike.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4138,10 +4141,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118916530</v>
+        <v>118916498</v>
       </c>
       <c r="B32" t="n">
-        <v>97853</v>
+        <v>97876</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4150,30 +4153,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4182,10 +4185,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533541</v>
+        <v>533378</v>
       </c>
       <c r="R32" t="n">
-        <v>6831281</v>
+        <v>6831359</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4212,27 +4215,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1 blommande.</t>
+          <t>8 blommande.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4259,7 +4262,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118916533</v>
+        <v>118916537</v>
       </c>
       <c r="B33" t="n">
         <v>97853</v>
@@ -4294,19 +4297,19 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Vitmossamyren, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533803</v>
+        <v>533332</v>
       </c>
       <c r="R33" t="n">
-        <v>6831153</v>
+        <v>6831225</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4333,27 +4336,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>5 blommande.</t>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4380,10 +4383,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118916513</v>
+        <v>118916535</v>
       </c>
       <c r="B34" t="n">
-        <v>97874</v>
+        <v>97853</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4392,38 +4395,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533654</v>
+        <v>533413</v>
       </c>
       <c r="R34" t="n">
-        <v>6831286</v>
+        <v>6831326</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4450,22 +4457,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>5 blommande</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4492,10 +4504,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118916550</v>
+        <v>118916513</v>
       </c>
       <c r="B35" t="n">
-        <v>78491</v>
+        <v>97874</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4504,25 +4516,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4532,10 +4544,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533799</v>
+        <v>533654</v>
       </c>
       <c r="R35" t="n">
-        <v>6831165</v>
+        <v>6831286</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4567,7 +4579,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4577,7 +4589,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4604,10 +4616,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118916522</v>
+        <v>118916514</v>
       </c>
       <c r="B36" t="n">
-        <v>79572</v>
+        <v>97874</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4616,25 +4628,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4644,7 +4656,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533734</v>
+        <v>533735</v>
       </c>
       <c r="R36" t="n">
         <v>6831167</v>
@@ -4700,21 +4712,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4731,10 +4728,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118916527</v>
+        <v>118916515</v>
       </c>
       <c r="B37" t="n">
-        <v>79572</v>
+        <v>97874</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4743,25 +4740,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4771,10 +4768,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533429</v>
+        <v>533342</v>
       </c>
       <c r="R37" t="n">
-        <v>6831320</v>
+        <v>6831321</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4806,7 +4803,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4816,7 +4813,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4843,10 +4840,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118916549</v>
+        <v>118916506</v>
       </c>
       <c r="B38" t="n">
-        <v>78491</v>
+        <v>103356</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4855,38 +4852,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>222412</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533754</v>
+        <v>533367</v>
       </c>
       <c r="R38" t="n">
-        <v>6831152</v>
+        <v>6831370</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4913,22 +4914,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4955,10 +4956,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118916565</v>
+        <v>118916532</v>
       </c>
       <c r="B39" t="n">
-        <v>97770</v>
+        <v>97853</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4967,30 +4968,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4999,10 +5000,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533438</v>
+        <v>533718</v>
       </c>
       <c r="R39" t="n">
-        <v>6831366</v>
+        <v>6831195</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5029,22 +5030,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5071,10 +5072,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118916525</v>
+        <v>118916495</v>
       </c>
       <c r="B40" t="n">
-        <v>79572</v>
+        <v>97876</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5083,38 +5084,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533807</v>
+        <v>533459</v>
       </c>
       <c r="R40" t="n">
-        <v>6831175</v>
+        <v>6831324</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5146,7 +5151,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5156,7 +5161,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5183,10 +5188,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118916498</v>
+        <v>118916503</v>
       </c>
       <c r="B41" t="n">
-        <v>97876</v>
+        <v>56502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5199,26 +5204,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219847</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5227,10 +5232,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533378</v>
+        <v>533551</v>
       </c>
       <c r="R41" t="n">
-        <v>6831359</v>
+        <v>6831256</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5257,27 +5262,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>8 blommande.</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5304,10 +5304,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118916539</v>
+        <v>118916496</v>
       </c>
       <c r="B42" t="n">
-        <v>97853</v>
+        <v>97876</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5316,30 +5316,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5348,10 +5348,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533379</v>
+        <v>533706</v>
       </c>
       <c r="R42" t="n">
-        <v>6831342</v>
+        <v>6831172</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5378,27 +5378,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>15 blommande.</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5425,10 +5420,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118916562</v>
+        <v>118916517</v>
       </c>
       <c r="B43" t="n">
-        <v>97770</v>
+        <v>97874</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5441,21 +5436,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5465,10 +5460,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533755</v>
+        <v>533438</v>
       </c>
       <c r="R43" t="n">
-        <v>6831181</v>
+        <v>6831363</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5495,22 +5490,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5537,7 +5532,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118916540</v>
+        <v>118916538</v>
       </c>
       <c r="B44" t="n">
         <v>97853</v>
@@ -5570,17 +5565,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533370</v>
+        <v>533361</v>
       </c>
       <c r="R44" t="n">
-        <v>6831353</v>
+        <v>6831321</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5612,7 +5611,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5622,12 +5621,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>4 blommande.</t>
+          <t>1 blommande.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5654,7 +5653,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118916532</v>
+        <v>118916531</v>
       </c>
       <c r="B45" t="n">
         <v>97853</v>
@@ -5689,19 +5688,19 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Grustaget, Bläckhornsvägen, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533718</v>
+        <v>533488</v>
       </c>
       <c r="R45" t="n">
-        <v>6831195</v>
+        <v>6831349</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5733,7 +5732,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5743,7 +5742,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>12 blommande</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5770,10 +5774,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118916496</v>
+        <v>118916553</v>
       </c>
       <c r="B46" t="n">
-        <v>97876</v>
+        <v>78491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5782,42 +5786,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533706</v>
+        <v>533388</v>
       </c>
       <c r="R46" t="n">
-        <v>6831172</v>
+        <v>6831360</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5844,22 +5844,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5870,6 +5870,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5886,10 +5901,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118916505</v>
+        <v>118916552</v>
       </c>
       <c r="B47" t="n">
-        <v>56502</v>
+        <v>78491</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5898,43 +5913,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533330</v>
+        <v>533316</v>
       </c>
       <c r="R47" t="n">
-        <v>6831362</v>
+        <v>6831283</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5966,7 +5976,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5976,7 +5986,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6003,10 +6013,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118916526</v>
+        <v>118916549</v>
       </c>
       <c r="B48" t="n">
-        <v>79572</v>
+        <v>78491</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6019,21 +6029,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6043,10 +6053,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533233</v>
+        <v>533754</v>
       </c>
       <c r="R48" t="n">
-        <v>6831210</v>
+        <v>6831152</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6073,22 +6083,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6115,10 +6125,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118916537</v>
+        <v>118916559</v>
       </c>
       <c r="B49" t="n">
-        <v>97853</v>
+        <v>97770</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6127,42 +6137,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vitmossamyren, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533332</v>
+        <v>533639</v>
       </c>
       <c r="R49" t="n">
-        <v>6831225</v>
+        <v>6831171</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6189,27 +6195,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>4 blommande.</t>
+          <t>Riklig förekomst i dike.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6236,10 +6242,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118916552</v>
+        <v>118916516</v>
       </c>
       <c r="B50" t="n">
-        <v>78491</v>
+        <v>97874</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6248,25 +6254,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6276,10 +6282,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533316</v>
+        <v>533391</v>
       </c>
       <c r="R50" t="n">
-        <v>6831283</v>
+        <v>6831356</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6311,7 +6317,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6321,7 +6327,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6348,10 +6359,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118916524</v>
+        <v>118916546</v>
       </c>
       <c r="B51" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6360,38 +6371,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533742</v>
+        <v>533428</v>
       </c>
       <c r="R51" t="n">
-        <v>6831175</v>
+        <v>6831326</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6418,22 +6433,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>16 blommande.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6444,21 +6464,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6475,10 +6480,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118916503</v>
+        <v>118916497</v>
       </c>
       <c r="B52" t="n">
-        <v>56502</v>
+        <v>97876</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6491,26 +6496,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6519,10 +6524,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533551</v>
+        <v>533366</v>
       </c>
       <c r="R52" t="n">
-        <v>6831256</v>
+        <v>6831375</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6549,22 +6554,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6591,10 +6596,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118916514</v>
+        <v>118916551</v>
       </c>
       <c r="B53" t="n">
-        <v>97874</v>
+        <v>78491</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6603,25 +6608,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6631,10 +6636,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533735</v>
+        <v>533202</v>
       </c>
       <c r="R53" t="n">
-        <v>6831167</v>
+        <v>6831238</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6661,22 +6666,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6703,10 +6708,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118916506</v>
+        <v>118916520</v>
       </c>
       <c r="B54" t="n">
-        <v>103356</v>
+        <v>97887</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6719,38 +6724,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222412</v>
+        <v>219874</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533367</v>
+        <v>533754</v>
       </c>
       <c r="R54" t="n">
-        <v>6831370</v>
+        <v>6831162</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6777,22 +6778,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Under gammal sälg.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6819,10 +6825,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118916553</v>
+        <v>118916541</v>
       </c>
       <c r="B55" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6831,38 +6837,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533388</v>
+        <v>533394</v>
       </c>
       <c r="R55" t="n">
-        <v>6831360</v>
+        <v>6831359</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6894,7 +6904,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6904,7 +6914,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6915,21 +6930,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -6949,11 +6949,11 @@
         <v>119306222</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>57357</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -2995,7 +2995,7 @@
         <v>118916562</v>
       </c>
       <c r="B22" t="n">
-        <v>97775</v>
+        <v>98092</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>118916565</v>
       </c>
       <c r="B30" t="n">
-        <v>97775</v>
+        <v>98092</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>118916558</v>
       </c>
       <c r="B33" t="n">
-        <v>97775</v>
+        <v>98092</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>118916560</v>
       </c>
       <c r="B34" t="n">
-        <v>97775</v>
+        <v>98092</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>118916563</v>
       </c>
       <c r="B37" t="n">
-        <v>97775</v>
+        <v>98092</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>118916559</v>
       </c>
       <c r="B49" t="n">
-        <v>97775</v>
+        <v>98092</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -2995,7 +2995,7 @@
         <v>118916562</v>
       </c>
       <c r="B22" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>118916565</v>
       </c>
       <c r="B30" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>118916558</v>
       </c>
       <c r="B33" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>118916560</v>
       </c>
       <c r="B34" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>118916563</v>
       </c>
       <c r="B37" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>118916559</v>
       </c>
       <c r="B49" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -2995,7 +2995,7 @@
         <v>118916562</v>
       </c>
       <c r="B22" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>118916565</v>
       </c>
       <c r="B30" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>118916558</v>
       </c>
       <c r="B33" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>118916560</v>
       </c>
       <c r="B34" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>118916563</v>
       </c>
       <c r="B37" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>118916559</v>
       </c>
       <c r="B49" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -2995,7 +2995,7 @@
         <v>118916562</v>
       </c>
       <c r="B22" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>118916565</v>
       </c>
       <c r="B30" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>118916558</v>
       </c>
       <c r="B33" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>118916560</v>
       </c>
       <c r="B34" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>118916563</v>
       </c>
       <c r="B37" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>118916559</v>
       </c>
       <c r="B49" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -2995,7 +2995,7 @@
         <v>118916562</v>
       </c>
       <c r="B22" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3009,11 +3009,6 @@
       </c>
       <c r="E22" t="n">
         <v>219790</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3928,7 +3923,7 @@
         <v>118916565</v>
       </c>
       <c r="B30" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3942,11 +3937,6 @@
       </c>
       <c r="E30" t="n">
         <v>219790</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4281,7 +4271,7 @@
         <v>118916558</v>
       </c>
       <c r="B33" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4295,11 +4285,6 @@
       </c>
       <c r="E33" t="n">
         <v>219790</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4393,7 +4378,7 @@
         <v>118916560</v>
       </c>
       <c r="B34" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4407,11 +4392,6 @@
       </c>
       <c r="E34" t="n">
         <v>219790</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4747,7 +4727,7 @@
         <v>118916563</v>
       </c>
       <c r="B37" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4761,11 +4741,6 @@
       </c>
       <c r="E37" t="n">
         <v>219790</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6140,7 +6115,7 @@
         <v>118916559</v>
       </c>
       <c r="B49" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6154,11 +6129,6 @@
       </c>
       <c r="E49" t="n">
         <v>219790</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -2995,7 +2995,7 @@
         <v>118916562</v>
       </c>
       <c r="B22" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3009,6 +3009,11 @@
       </c>
       <c r="E22" t="n">
         <v>219790</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3923,7 +3928,7 @@
         <v>118916565</v>
       </c>
       <c r="B30" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3937,6 +3942,11 @@
       </c>
       <c r="E30" t="n">
         <v>219790</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4271,7 +4281,7 @@
         <v>118916558</v>
       </c>
       <c r="B33" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4285,6 +4295,11 @@
       </c>
       <c r="E33" t="n">
         <v>219790</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4378,7 +4393,7 @@
         <v>118916560</v>
       </c>
       <c r="B34" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4392,6 +4407,11 @@
       </c>
       <c r="E34" t="n">
         <v>219790</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4727,7 +4747,7 @@
         <v>118916563</v>
       </c>
       <c r="B37" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4741,6 +4761,11 @@
       </c>
       <c r="E37" t="n">
         <v>219790</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6115,7 +6140,7 @@
         <v>118916559</v>
       </c>
       <c r="B49" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6129,6 +6154,11 @@
       </c>
       <c r="E49" t="n">
         <v>219790</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -2995,7 +2995,7 @@
         <v>118916562</v>
       </c>
       <c r="B22" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>118916565</v>
       </c>
       <c r="B30" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>118916558</v>
       </c>
       <c r="B33" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>118916560</v>
       </c>
       <c r="B34" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>118916563</v>
       </c>
       <c r="B37" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>118916559</v>
       </c>
       <c r="B49" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -2995,7 +2995,7 @@
         <v>118916562</v>
       </c>
       <c r="B22" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>118916565</v>
       </c>
       <c r="B30" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>118916558</v>
       </c>
       <c r="B33" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>118916560</v>
       </c>
       <c r="B34" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>118916563</v>
       </c>
       <c r="B37" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>118916559</v>
       </c>
       <c r="B49" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -2995,7 +2995,7 @@
         <v>118916562</v>
       </c>
       <c r="B22" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>118916565</v>
       </c>
       <c r="B30" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>118916558</v>
       </c>
       <c r="B33" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>118916560</v>
       </c>
       <c r="B34" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>118916563</v>
       </c>
       <c r="B37" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>118916559</v>
       </c>
       <c r="B49" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -2995,7 +2995,7 @@
         <v>118916562</v>
       </c>
       <c r="B22" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>118916565</v>
       </c>
       <c r="B30" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>118916558</v>
       </c>
       <c r="B33" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>118916560</v>
       </c>
       <c r="B34" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>118916563</v>
       </c>
       <c r="B37" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>118916559</v>
       </c>
       <c r="B49" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -6949,7 +6949,7 @@
         <v>119306222</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2019 artfynd.xlsx
+++ b/artfynd/A 45004-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112606427</v>
+        <v>118916513</v>
       </c>
       <c r="B6" t="n">
-        <v>78919</v>
+        <v>97879</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,41 +1155,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öjung, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533431</v>
+        <v>533654</v>
       </c>
       <c r="R6" t="n">
-        <v>6831321</v>
+        <v>6831286</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,17 +1213,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112606426</v>
+        <v>118916537</v>
       </c>
       <c r="B7" t="n">
-        <v>78919</v>
+        <v>97858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,41 +1267,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öjung, Hls</t>
+          <t>Vitmossamyren, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533557</v>
+        <v>533332</v>
       </c>
       <c r="R7" t="n">
-        <v>6831226</v>
+        <v>6831225</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,17 +1329,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1364,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112606429</v>
+        <v>118916543</v>
       </c>
       <c r="B8" t="n">
-        <v>77608</v>
+        <v>97858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,41 +1388,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öjung, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533290</v>
+        <v>533408</v>
       </c>
       <c r="R8" t="n">
-        <v>6831189</v>
+        <v>6831362</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,17 +1450,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>35 blommande.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,22 +1485,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112606424</v>
+        <v>118916528</v>
       </c>
       <c r="B9" t="n">
-        <v>78919</v>
+        <v>97762</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,41 +1509,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öjung, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533738</v>
+        <v>533643</v>
       </c>
       <c r="R9" t="n">
-        <v>6831180</v>
+        <v>6831218</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,17 +1571,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,22 +1601,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916513</v>
+        <v>118916498</v>
       </c>
       <c r="B10" t="n">
-        <v>97879</v>
+        <v>97881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,34 +1629,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533654</v>
+        <v>533378</v>
       </c>
       <c r="R10" t="n">
-        <v>6831286</v>
+        <v>6831359</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1641,22 +1687,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>8 blommande.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916537</v>
+        <v>118916524</v>
       </c>
       <c r="B11" t="n">
-        <v>97858</v>
+        <v>79574</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,42 +1746,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vitmossamyren, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533332</v>
+        <v>533742</v>
       </c>
       <c r="R11" t="n">
-        <v>6831225</v>
+        <v>6831175</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1757,27 +1804,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4 blommande.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,6 +1830,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1804,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916543</v>
+        <v>118916551</v>
       </c>
       <c r="B12" t="n">
-        <v>97858</v>
+        <v>78493</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,42 +1873,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533408</v>
+        <v>533202</v>
       </c>
       <c r="R12" t="n">
-        <v>6831362</v>
+        <v>6831238</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1883,7 +1936,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,12 +1946,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>35 blommande.</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916528</v>
+        <v>118916550</v>
       </c>
       <c r="B13" t="n">
-        <v>97762</v>
+        <v>78493</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1937,42 +1985,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533643</v>
+        <v>533799</v>
       </c>
       <c r="R13" t="n">
-        <v>6831218</v>
+        <v>6831165</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2004,7 +2048,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2058,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916498</v>
+        <v>118916519</v>
       </c>
       <c r="B14" t="n">
-        <v>97881</v>
+        <v>97892</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,38 +2101,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>219874</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Grustaget, Bläckhornsvägen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533378</v>
+        <v>533490</v>
       </c>
       <c r="R14" t="n">
-        <v>6831359</v>
+        <v>6831352</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2115,27 +2159,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>8 blommande.</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916524</v>
+        <v>118916546</v>
       </c>
       <c r="B15" t="n">
-        <v>79574</v>
+        <v>97858</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,38 +2213,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533742</v>
+        <v>533428</v>
       </c>
       <c r="R15" t="n">
-        <v>6831175</v>
+        <v>6831326</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2232,22 +2275,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>16 blommande.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,21 +2306,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2289,10 +2322,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118916551</v>
+        <v>118916530</v>
       </c>
       <c r="B16" t="n">
-        <v>78493</v>
+        <v>97858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,38 +2334,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533202</v>
+        <v>533541</v>
       </c>
       <c r="R16" t="n">
-        <v>6831238</v>
+        <v>6831281</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2359,22 +2396,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 blommande.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2443,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118916550</v>
+        <v>118916539</v>
       </c>
       <c r="B17" t="n">
-        <v>78493</v>
+        <v>97858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,38 +2455,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533799</v>
+        <v>533379</v>
       </c>
       <c r="R17" t="n">
-        <v>6831165</v>
+        <v>6831342</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2471,22 +2517,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>15 blommande.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,10 +2564,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118916519</v>
+        <v>118916562</v>
       </c>
       <c r="B18" t="n">
-        <v>97892</v>
+        <v>98264</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,38 +2580,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grustaget, Bläckhornsvägen, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533490</v>
+        <v>533755</v>
       </c>
       <c r="R18" t="n">
-        <v>6831352</v>
+        <v>6831181</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2592,7 +2639,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2602,7 +2649,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,10 +2676,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118916546</v>
+        <v>118916499</v>
       </c>
       <c r="B19" t="n">
-        <v>97858</v>
+        <v>97881</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,30 +2688,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2673,10 +2720,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533428</v>
+        <v>533418</v>
       </c>
       <c r="R19" t="n">
-        <v>6831326</v>
+        <v>6831358</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2708,7 +2755,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,12 +2765,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>16 blommande.</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,10 +2792,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118916530</v>
+        <v>118916514</v>
       </c>
       <c r="B20" t="n">
-        <v>97858</v>
+        <v>97879</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2762,42 +2804,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533541</v>
+        <v>533735</v>
       </c>
       <c r="R20" t="n">
-        <v>6831281</v>
+        <v>6831167</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2829,7 +2867,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2839,12 +2877,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>1 blommande.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2871,7 +2904,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118916539</v>
+        <v>118916532</v>
       </c>
       <c r="B21" t="n">
         <v>97858</v>
@@ -2906,7 +2939,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2915,10 +2948,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533379</v>
+        <v>533718</v>
       </c>
       <c r="R21" t="n">
-        <v>6831342</v>
+        <v>6831195</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2945,27 +2978,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>15 blommande.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2992,10 +3020,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118916562</v>
+        <v>118916533</v>
       </c>
       <c r="B22" t="n">
-        <v>98264</v>
+        <v>97858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3004,38 +3032,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533755</v>
+        <v>533803</v>
       </c>
       <c r="R22" t="n">
-        <v>6831181</v>
+        <v>6831153</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3067,7 +3099,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3077,7 +3109,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 blommande.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3104,10 +3141,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118916499</v>
+        <v>118916553</v>
       </c>
       <c r="B23" t="n">
-        <v>97881</v>
+        <v>78493</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3116,42 +3153,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533418</v>
+        <v>533388</v>
       </c>
       <c r="R23" t="n">
-        <v>6831358</v>
+        <v>6831360</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3183,7 +3216,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3226,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3204,6 +3237,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3220,10 +3268,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118916514</v>
+        <v>118916526</v>
       </c>
       <c r="B24" t="n">
-        <v>97879</v>
+        <v>79574</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3232,25 +3280,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3260,10 +3308,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533735</v>
+        <v>533233</v>
       </c>
       <c r="R24" t="n">
-        <v>6831167</v>
+        <v>6831210</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3290,22 +3338,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3332,10 +3380,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118916532</v>
+        <v>118916505</v>
       </c>
       <c r="B25" t="n">
-        <v>97858</v>
+        <v>56504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3344,30 +3392,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3376,10 +3425,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533718</v>
+        <v>533330</v>
       </c>
       <c r="R25" t="n">
-        <v>6831195</v>
+        <v>6831362</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3406,22 +3455,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3448,10 +3497,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118916533</v>
+        <v>118916565</v>
       </c>
       <c r="B26" t="n">
-        <v>97858</v>
+        <v>98264</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,30 +3509,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3492,10 +3541,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533803</v>
+        <v>533438</v>
       </c>
       <c r="R26" t="n">
-        <v>6831153</v>
+        <v>6831366</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3522,27 +3571,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>5 blommande.</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,10 +3613,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118916553</v>
+        <v>118916531</v>
       </c>
       <c r="B27" t="n">
-        <v>78493</v>
+        <v>97858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,38 +3625,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Grustaget, Bläckhornsvägen, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533388</v>
+        <v>533488</v>
       </c>
       <c r="R27" t="n">
-        <v>6831360</v>
+        <v>6831349</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3639,22 +3687,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>12 blommande</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,21 +3718,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3696,10 +3734,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118916526</v>
+        <v>118916506</v>
       </c>
       <c r="B28" t="n">
-        <v>79574</v>
+        <v>103361</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3708,38 +3746,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533233</v>
+        <v>533367</v>
       </c>
       <c r="R28" t="n">
-        <v>6831210</v>
+        <v>6831370</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3771,7 +3813,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3781,7 +3823,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3808,10 +3850,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118916505</v>
+        <v>118916558</v>
       </c>
       <c r="B29" t="n">
-        <v>56504</v>
+        <v>98264</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3824,39 +3866,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533330</v>
+        <v>533706</v>
       </c>
       <c r="R29" t="n">
-        <v>6831362</v>
+        <v>6831271</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3883,22 +3920,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3925,7 +3962,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118916565</v>
+        <v>118916560</v>
       </c>
       <c r="B30" t="n">
         <v>98264</v>
@@ -3958,21 +3995,17 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533438</v>
+        <v>533732</v>
       </c>
       <c r="R30" t="n">
-        <v>6831366</v>
+        <v>6831163</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3999,22 +4032,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4041,7 +4074,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118916531</v>
+        <v>118916535</v>
       </c>
       <c r="B31" t="n">
         <v>97858</v>
@@ -4076,19 +4109,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grustaget, Bläckhornsvägen, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533488</v>
+        <v>533413</v>
       </c>
       <c r="R31" t="n">
-        <v>6831349</v>
+        <v>6831326</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4115,27 +4148,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>12 blommande</t>
+          <t>5 blommande</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4162,10 +4195,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118916506</v>
+        <v>118916541</v>
       </c>
       <c r="B32" t="n">
-        <v>103361</v>
+        <v>97858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4174,30 +4207,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4206,10 +4239,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533367</v>
+        <v>533394</v>
       </c>
       <c r="R32" t="n">
-        <v>6831370</v>
+        <v>6831359</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4241,7 +4274,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4251,7 +4284,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4278,7 +4316,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118916558</v>
+        <v>118916563</v>
       </c>
       <c r="B33" t="n">
         <v>98264</v>
@@ -4318,10 +4356,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533706</v>
+        <v>533835</v>
       </c>
       <c r="R33" t="n">
-        <v>6831271</v>
+        <v>6831191</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4353,7 +4391,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4363,7 +4401,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4390,10 +4428,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118916560</v>
+        <v>118916496</v>
       </c>
       <c r="B34" t="n">
-        <v>98264</v>
+        <v>97881</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4406,34 +4444,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533732</v>
+        <v>533706</v>
       </c>
       <c r="R34" t="n">
-        <v>6831163</v>
+        <v>6831172</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4465,7 +4507,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4475,7 +4517,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4502,10 +4544,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118916535</v>
+        <v>118916516</v>
       </c>
       <c r="B35" t="n">
-        <v>97858</v>
+        <v>97879</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4514,42 +4556,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533413</v>
+        <v>533391</v>
       </c>
       <c r="R35" t="n">
-        <v>6831326</v>
+        <v>6831356</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4581,7 +4619,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4591,12 +4629,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>5 blommande</t>
+          <t>Riklig förekomst.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4623,10 +4661,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118916541</v>
+        <v>118916495</v>
       </c>
       <c r="B36" t="n">
-        <v>97858</v>
+        <v>97881</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4635,30 +4673,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4667,10 +4705,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533394</v>
+        <v>533459</v>
       </c>
       <c r="R36" t="n">
-        <v>6831359</v>
+        <v>6831324</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4697,27 +4735,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>4 blommande.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4744,10 +4777,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118916563</v>
+        <v>118916536</v>
       </c>
       <c r="B37" t="n">
-        <v>98264</v>
+        <v>97858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4756,38 +4789,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Vitmossamyren, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533835</v>
+        <v>533335</v>
       </c>
       <c r="R37" t="n">
-        <v>6831191</v>
+        <v>6831217</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4814,22 +4851,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>10 blommande</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4856,10 +4898,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118916496</v>
+        <v>118916540</v>
       </c>
       <c r="B38" t="n">
-        <v>97881</v>
+        <v>97858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4868,42 +4910,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533706</v>
+        <v>533370</v>
       </c>
       <c r="R38" t="n">
-        <v>6831172</v>
+        <v>6831353</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4930,22 +4968,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>4 blommande.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4972,10 +5015,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118916516</v>
+        <v>118916503</v>
       </c>
       <c r="B39" t="n">
-        <v>97879</v>
+        <v>56504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4988,34 +5031,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533391</v>
+        <v>533551</v>
       </c>
       <c r="R39" t="n">
-        <v>6831356</v>
+        <v>6831256</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5042,27 +5089,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5089,10 +5131,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118916495</v>
+        <v>118916520</v>
       </c>
       <c r="B40" t="n">
-        <v>97881</v>
+        <v>97892</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5105,38 +5147,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219847</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533459</v>
+        <v>533754</v>
       </c>
       <c r="R40" t="n">
-        <v>6831324</v>
+        <v>6831162</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5168,7 +5206,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5178,7 +5216,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Under gammal sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5205,10 +5248,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118916536</v>
+        <v>118916525</v>
       </c>
       <c r="B41" t="n">
-        <v>97858</v>
+        <v>79574</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5217,42 +5260,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vitmossamyren, Hls</t>
+          <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533335</v>
+        <v>533807</v>
       </c>
       <c r="R41" t="n">
-        <v>6831217</v>
+        <v>6831175</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5279,27 +5318,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>10 blommande</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5326,10 +5360,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118916540</v>
+        <v>118916497</v>
       </c>
       <c r="B42" t="n">
-        <v>97858</v>
+        <v>97881</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5338,38 +5372,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533370</v>
+        <v>533366</v>
       </c>
       <c r="R42" t="n">
-        <v>6831353</v>
+        <v>6831375</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5401,7 +5439,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5411,12 +5449,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>4 blommande.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5443,10 +5476,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118916503</v>
+        <v>118916538</v>
       </c>
       <c r="B43" t="n">
-        <v>56504</v>
+        <v>97858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5455,30 +5488,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5487,10 +5520,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533551</v>
+        <v>533361</v>
       </c>
       <c r="R43" t="n">
-        <v>6831256</v>
+        <v>6831321</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5517,22 +5550,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 blommande.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5559,10 +5597,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118916520</v>
+        <v>118916549</v>
       </c>
       <c r="B44" t="n">
-        <v>97892</v>
+        <v>78493</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5571,25 +5609,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5602,7 +5640,7 @@
         <v>533754</v>
       </c>
       <c r="R44" t="n">
-        <v>6831162</v>
+        <v>6831152</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5634,7 +5672,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5644,12 +5682,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Under gammal sälg.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5676,10 +5709,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118916525</v>
+        <v>118916559</v>
       </c>
       <c r="B45" t="n">
-        <v>79574</v>
+        <v>98264</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5688,25 +5721,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5716,10 +5749,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533807</v>
+        <v>533639</v>
       </c>
       <c r="R45" t="n">
-        <v>6831175</v>
+        <v>6831171</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5751,7 +5784,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5761,7 +5794,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i dike.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5788,10 +5826,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118916497</v>
+        <v>118916504</v>
       </c>
       <c r="B46" t="n">
-        <v>97881</v>
+        <v>56504</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5804,26 +5842,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219847</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5832,10 +5871,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533366</v>
+        <v>533329</v>
       </c>
       <c r="R46" t="n">
-        <v>6831375</v>
+        <v>6831299</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5867,7 +5906,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5877,7 +5916,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5904,10 +5943,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118916538</v>
+        <v>118916527</v>
       </c>
       <c r="B47" t="n">
-        <v>97858</v>
+        <v>79574</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5916,42 +5955,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533361</v>
+        <v>533429</v>
       </c>
       <c r="R47" t="n">
-        <v>6831321</v>
+        <v>6831320</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5983,7 +6018,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5993,12 +6028,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:02</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 blommande.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6025,7 +6055,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118916549</v>
+        <v>118916552</v>
       </c>
       <c r="B48" t="n">
         <v>78493</v>
@@ -6065,10 +6095,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533754</v>
+        <v>533316</v>
       </c>
       <c r="R48" t="n">
-        <v>6831152</v>
+        <v>6831283</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6095,22 +6125,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6137,10 +6167,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118916559</v>
+        <v>118916522</v>
       </c>
       <c r="B49" t="n">
-        <v>98264</v>
+        <v>79574</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6149,25 +6179,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6177,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533639</v>
+        <v>533734</v>
       </c>
       <c r="R49" t="n">
-        <v>6831171</v>
+        <v>6831167</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6212,7 +6242,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6222,12 +6252,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i dike.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6238,6 +6263,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6254,10 +6294,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118916504</v>
+        <v>118916517</v>
       </c>
       <c r="B50" t="n">
-        <v>56504</v>
+        <v>97879</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6270,39 +6310,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533329</v>
+        <v>533438</v>
       </c>
       <c r="R50" t="n">
-        <v>6831299</v>
+        <v>6831363</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6334,7 +6369,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6344,7 +6379,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6371,10 +6406,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118916527</v>
+        <v>118916515</v>
       </c>
       <c r="B51" t="n">
-        <v>79574</v>
+        <v>97879</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6383,25 +6418,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6411,10 +6446,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533429</v>
+        <v>533342</v>
       </c>
       <c r="R51" t="n">
-        <v>6831320</v>
+        <v>6831321</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6446,7 +6481,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6456,7 +6491,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6483,10 +6518,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118916552</v>
+        <v>119306222</v>
       </c>
       <c r="B52" t="n">
-        <v>78493</v>
+        <v>57481</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6499,34 +6534,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
+          <t>Bläckhornsvägen, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533316</v>
+        <v>533344</v>
       </c>
       <c r="R52" t="n">
-        <v>6831283</v>
+        <v>6831378</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6553,22 +6596,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6595,10 +6628,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118916522</v>
+        <v>119306277</v>
       </c>
       <c r="B53" t="n">
-        <v>79574</v>
+        <v>97907</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6607,38 +6640,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lindsbergsmyrabäcken, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533734</v>
+        <v>533423</v>
       </c>
       <c r="R53" t="n">
-        <v>6831167</v>
+        <v>6831367</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6665,22 +6710,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>57 blommande.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6689,23 +6729,9 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6719,460 +6745,6 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>118916517</v>
-      </c>
-      <c r="B54" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>533438</v>
-      </c>
-      <c r="R54" t="n">
-        <v>6831363</v>
-      </c>
-      <c r="S54" t="n">
-        <v>25</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Ovanåker</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Ovanåker</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Gustav Forsblom</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Gustav Forsblom</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>118916515</v>
-      </c>
-      <c r="B55" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>533342</v>
-      </c>
-      <c r="R55" t="n">
-        <v>6831321</v>
-      </c>
-      <c r="S55" t="n">
-        <v>25</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Ovanåker</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Ovanåker</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Gustav Forsblom</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Gustav Forsblom</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>119306222</v>
-      </c>
-      <c r="B56" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Bläckhornsvägen, Hls</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>533344</v>
-      </c>
-      <c r="R56" t="n">
-        <v>6831378</v>
-      </c>
-      <c r="S56" t="n">
-        <v>25</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Ovanåker</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Ovanåker</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Gustav Forsblom</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Gustav Forsblom</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>119306277</v>
-      </c>
-      <c r="B57" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Lindsbergsmyrabäcken, Hls</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>533423</v>
-      </c>
-      <c r="R57" t="n">
-        <v>6831367</v>
-      </c>
-      <c r="S57" t="n">
-        <v>25</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Ovanåker</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Ovanåker</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>57 blommande.</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Gustav Forsblom</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Gustav Forsblom</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
